--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484197_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484197_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.7286</v>
+        <v>8.2822</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3547</v>
+        <v>6.0486</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3739</v>
+        <v>2.2336</v>
       </c>
       <c r="G2" t="n">
         <v>5.818</v>
@@ -610,13 +610,13 @@
         <v>2.3806</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6773</v>
+        <v>0.231</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3119</v>
+        <v>0.0058</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3654</v>
+        <v>0.2252</v>
       </c>
       <c r="V2" t="n">
         <v>0.8445</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3046</v>
+        <v>3.7944</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1215</v>
+        <v>2.6113</v>
       </c>
       <c r="F3" t="n">
         <v>1.1831</v>
@@ -688,10 +688,10 @@
         <v>1.3887</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2607</v>
+        <v>-0.2494</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6236</v>
+        <v>0.1135</v>
       </c>
       <c r="U3" t="n">
         <v>-0.3629</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8601</v>
+        <v>3.0182</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7894</v>
+        <v>2.8914</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0707</v>
+        <v>0.1268</v>
       </c>
       <c r="G4" t="n">
         <v>3.2336</v>
@@ -766,13 +766,13 @@
         <v>1.3887</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4331</v>
+        <v>-0.2749</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3004</v>
+        <v>-0.1983</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1327</v>
+        <v>-0.0766</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3373</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6279</v>
+        <v>2.3141</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0028</v>
+        <v>1.4927</v>
       </c>
       <c r="F5" t="n">
-        <v>0.625</v>
+        <v>0.8214</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4549</v>
@@ -844,13 +844,13 @@
         <v>2.579</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8962</v>
+        <v>0.5824</v>
       </c>
       <c r="T5" t="n">
-        <v>0.873</v>
+        <v>0.3628</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0232</v>
+        <v>0.2196</v>
       </c>
       <c r="V5" t="n">
         <v>0.7979000000000001</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.505</v>
+        <v>1.4973</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3629</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8679</v>
+        <v>2.0643</v>
       </c>
       <c r="G6" t="n">
         <v>1.4227</v>
@@ -922,13 +922,13 @@
         <v>1.7855</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4994</v>
+        <v>0.4917</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4366</v>
+        <v>0.2325</v>
       </c>
       <c r="U6" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.2592</v>
       </c>
       <c r="V6" t="n">
         <v>0.7733</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0233</v>
+        <v>0.4213</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0947</v>
+        <v>-0.5845</v>
       </c>
       <c r="F7" t="n">
-        <v>1.118</v>
+        <v>1.0058</v>
       </c>
       <c r="G7" t="n">
         <v>0.7145</v>
@@ -1000,13 +1000,13 @@
         <v>1.9838</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3186</v>
+        <v>0.0793</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.289</v>
+        <v>0.2211</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0296</v>
+        <v>-0.1418</v>
       </c>
       <c r="V7" t="n">
         <v>1.8097</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8322000000000001</v>
+        <v>-0.7863</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8471</v>
+        <v>-0.745</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0148</v>
+        <v>-0.0413</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2454</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3208</v>
+        <v>-0.2749</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.187</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1338</v>
+        <v>-0.1899</v>
       </c>
       <c r="V8" t="n">
         <v>-0.266</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. WRIGHT</t>
+          <t>E. IBAEZ ALDAZABAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8589</v>
+        <v>-0.8159</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2391</v>
+        <v>-2.5899</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3802</v>
+        <v>1.774</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1888</v>
+        <v>-1.1526</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3755</v>
+        <v>-0.9478</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1867</v>
+        <v>-0.2048</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9016</v>
+        <v>-2.675</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.0622</v>
+        <v>-1.2394</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1606</v>
+        <v>-1.4356</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2872</v>
+        <v>1.5225</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3132</v>
+        <v>0.2916</v>
       </c>
       <c r="O9" t="n">
-        <v>0.026</v>
+        <v>1.2309</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1984</v>
+        <v>0.7935</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1822</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9838</v>
+        <v>0.7935</v>
       </c>
       <c r="S9" t="n">
-        <v>1.7594</v>
+        <v>-0.095</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2414</v>
+        <v>0.0851</v>
       </c>
       <c r="U9" t="n">
-        <v>0.518</v>
+        <v>-0.1801</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2311</v>
+        <v>-0.3619</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.8344</v>
+        <v>-0.3619</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. IBAEZ ALDAZABAL</t>
+          <t>T. WRIGHT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.048</v>
+        <v>-1.4252</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.794</v>
+        <v>-1.7493</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7459</v>
+        <v>0.3241</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1526</v>
+        <v>-1.1888</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9478</v>
+        <v>-1.3755</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2048</v>
+        <v>0.1867</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.675</v>
+        <v>-0.9016</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2394</v>
+        <v>-1.0622</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4356</v>
+        <v>0.1606</v>
       </c>
       <c r="M10" t="n">
-        <v>1.5225</v>
+        <v>-0.2872</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2916</v>
+        <v>-0.3132</v>
       </c>
       <c r="O10" t="n">
-        <v>1.2309</v>
+        <v>0.026</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7935</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.1822</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7935</v>
+        <v>1.9838</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3271</v>
+        <v>1.1931</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1189</v>
+        <v>0.7313</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2081</v>
+        <v>0.4618</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3619</v>
+        <v>-1.2311</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3619</v>
+        <v>-1.8344</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4112</v>
+        <v>-1.9572</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.063</v>
+        <v>-2.5528</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.5956</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0791</v>
@@ -1312,13 +1312,13 @@
         <v>0.9919</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1338</v>
+        <v>0.3202</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.238</v>
+        <v>0.2721</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1042</v>
+        <v>0.0481</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7175</v>
+        <v>-2.1615</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.679</v>
+        <v>-3.0669</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9615</v>
+        <v>0.9054</v>
       </c>
       <c r="G12" t="n">
         <v>-0.0618</v>
@@ -1390,13 +1390,13 @@
         <v>1.5871</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0091</v>
+        <v>0.547</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.0113</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6143</v>
+        <v>0.5582</v>
       </c>
       <c r="V12" t="n">
         <v>-0.266</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12.1817</v>
+        <v>12.1814</v>
       </c>
       <c r="E13" t="n">
-        <v>1.188599999999998</v>
+        <v>1.188600000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>10.9927</v>
+        <v>10.9928</v>
       </c>
       <c r="G13" t="n">
         <v>7.145999999999999</v>
@@ -1438,7 +1438,7 @@
         <v>11.1621</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.016300000000001</v>
+        <v>-4.0163</v>
       </c>
       <c r="J13" t="n">
         <v>9.419499999999999</v>
@@ -1453,7 +1453,7 @@
         <v>-2.2735</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4604</v>
+        <v>-0.4604000000000001</v>
       </c>
       <c r="O13" t="n">
         <v>-1.813</v>
@@ -1471,7 +1471,7 @@
         <v>2.5505</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7297</v>
+        <v>1.7296</v>
       </c>
       <c r="U13" t="n">
         <v>0.8208</v>
@@ -1480,16 +1480,16 @@
         <v>3.4768</v>
       </c>
       <c r="W13" t="n">
-        <v>7.8942</v>
+        <v>7.894200000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.4172</v>
+        <v>-4.417199999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. AMABILINO PEREZ</t>
+          <t>S. CASAÚ PUEYO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9473</v>
+        <v>1.4596</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3016</v>
+        <v>1.4827</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6456</v>
+        <v>-0.0231</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.9913</v>
+        <v>0.9298</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2576</v>
+        <v>0.4841</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.249</v>
+        <v>0.4457</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4302</v>
+        <v>1.8907</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3854</v>
+        <v>1.2054</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.9552</v>
+        <v>0.6853</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4216</v>
+        <v>-0.9609</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.1278</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7062</v>
+        <v>-0.2396</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3968</v>
+        <v>2.7774</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.3725</v>
+        <v>2.7774</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3252</v>
+        <v>-0.7751</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0375</v>
+        <v>-0.408</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2878</v>
+        <v>-0.3671</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2166</v>
+        <v>-1.4724</v>
       </c>
       <c r="W14" t="n">
-        <v>1.8097</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.5931</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. BONAZEBI LOUSSAKOU</t>
+          <t>M. GONZALEZ DE UBIETA BELLO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9174</v>
+        <v>1.4292</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5733</v>
+        <v>0.4805</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.656</v>
+        <v>0.9487</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4876</v>
+        <v>0.7786</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2116</v>
+        <v>0.1711</v>
       </c>
       <c r="I15" t="n">
-        <v>0.276</v>
+        <v>0.6075</v>
       </c>
       <c r="J15" t="n">
-        <v>2.404</v>
+        <v>1.546</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2836</v>
+        <v>1.094</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1205</v>
+        <v>0.452</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9164</v>
+        <v>-0.7674</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.072</v>
+        <v>-0.923</v>
       </c>
       <c r="O15" t="n">
         <v>0.1555</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1984</v>
+        <v>1.3887</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7855</v>
+        <v>2.3806</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7488</v>
+        <v>-0.3514</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5499000000000001</v>
+        <v>-0.0736</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1989</v>
+        <v>-0.2778</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1206</v>
+        <v>-0.3866</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.7239</v>
+        <v>-0.3866</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. GONZALEZ DE UBIETA BELLO</t>
+          <t>C. BONAZEBI LOUSSAKOU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7389</v>
+        <v>0.119</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1744</v>
+        <v>0.8591</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5644</v>
+        <v>-0.7401</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7786</v>
+        <v>0.4876</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1711</v>
+        <v>0.2116</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6075</v>
+        <v>0.276</v>
       </c>
       <c r="J16" t="n">
-        <v>1.546</v>
+        <v>2.404</v>
       </c>
       <c r="K16" t="n">
-        <v>1.094</v>
+        <v>2.2836</v>
       </c>
       <c r="L16" t="n">
-        <v>0.452</v>
+        <v>0.1205</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7674</v>
+        <v>-1.9164</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.923</v>
+        <v>-2.072</v>
       </c>
       <c r="O16" t="n">
         <v>0.1555</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3887</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3806</v>
+        <v>1.7855</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0418</v>
+        <v>-0.0496</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3797</v>
+        <v>-0.1643</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6621</v>
+        <v>0.1147</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3866</v>
+        <v>-0.1206</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3866</v>
+        <v>-0.7239</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. CASAÚ PUEYO</t>
+          <t>A. AMABILINO PEREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3331</v>
+        <v>-0.2957</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7685</v>
+        <v>-0.8207</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4354</v>
+        <v>0.5249</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9298</v>
+        <v>-0.9913</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4841</v>
+        <v>0.2576</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4457</v>
+        <v>-1.249</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8907</v>
+        <v>0.4302</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2054</v>
+        <v>2.3854</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6853</v>
+        <v>-1.9552</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9609</v>
+        <v>-1.4216</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-2.1278</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2396</v>
+        <v>0.7062</v>
       </c>
       <c r="P17" t="n">
-        <v>2.7774</v>
+        <v>0.3968</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7774</v>
+        <v>3.3725</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.9017</v>
+        <v>0.0822</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1222</v>
+        <v>-0.0849</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7795</v>
+        <v>0.1671</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.4724</v>
+        <v>0.2166</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.8097</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4724</v>
+        <v>-1.5931</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4581</v>
+        <v>-0.3101</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6012999999999999</v>
+        <v>-0.3972</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1432</v>
+        <v>0.0871</v>
       </c>
       <c r="G18" t="n">
         <v>-0.8113</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0873</v>
+        <v>0.2352</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.187</v>
+        <v>0.017</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2743</v>
+        <v>0.2182</v>
       </c>
       <c r="V18" t="n">
         <v>0.266</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. GUILLEN VIVES</t>
+          <t>A. PILAN PERET</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.871</v>
+        <v>-0.8627</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2924</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4214</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9482</v>
+        <v>0.9129</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5221</v>
+        <v>0.3778</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5739</v>
+        <v>0.5351</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1022</v>
+        <v>2.4342</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0106</v>
+        <v>1.1089</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1128</v>
+        <v>1.3253</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.846</v>
+        <v>-1.5213</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5327</v>
+        <v>-0.7311</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6867</v>
+        <v>-0.7902</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5952</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9838</v>
+        <v>-3.1741</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3887</v>
+        <v>2.1822</v>
       </c>
       <c r="S19" t="n">
-        <v>0.793</v>
+        <v>-0.4464</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7937</v>
+        <v>0.1361</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.5824</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1206</v>
+        <v>-0.3373</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1206</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. PILAN PERET</t>
+          <t>D. IRUELA RUBIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6491</v>
+        <v>-1.4176</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.582</v>
+        <v>-1.3161</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0671</v>
+        <v>-0.1015</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9129</v>
+        <v>-2.0513</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3778</v>
+        <v>-6.1633</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5351</v>
+        <v>4.112</v>
       </c>
       <c r="J20" t="n">
-        <v>2.4342</v>
+        <v>-0.5397</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1089</v>
+        <v>-3.557</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3253</v>
+        <v>3.0172</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5213</v>
+        <v>-1.5115</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7311</v>
+        <v>-2.6064</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7902</v>
+        <v>1.0948</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9919</v>
+        <v>1.5871</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.1741</v>
+        <v>-0.1984</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1822</v>
+        <v>1.7855</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2328</v>
+        <v>-0.2295</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3741</v>
+        <v>-0.578</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8588</v>
+        <v>0.3485</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3373</v>
+        <v>-0.7239</v>
       </c>
       <c r="W20" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8692</v>
+        <v>-0.7239</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. HAGENAERS COS</t>
+          <t>D. GUILLEN VIVES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1819</v>
+        <v>-1.501</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5024</v>
+        <v>-2.0066</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3205</v>
+        <v>0.5056</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.993</v>
+        <v>-0.9482</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.3027</v>
+        <v>-1.5221</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3097</v>
+        <v>0.5739</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.8895</v>
+        <v>-0.1022</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.0501</v>
+        <v>0.0106</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1606</v>
+        <v>-0.1128</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1035</v>
+        <v>-0.846</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2525</v>
+        <v>-1.5327</v>
       </c>
       <c r="O21" t="n">
-        <v>0.149</v>
+        <v>0.6867</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3968</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1822</v>
+        <v>-1.9838</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7855</v>
+        <v>1.3887</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2006</v>
+        <v>0.163</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3629</v>
+        <v>0.0795</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5635</v>
+        <v>0.0835</v>
       </c>
       <c r="V21" t="n">
-        <v>0.4085</v>
+        <v>-0.1206</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.1206</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. FEIXA MORANCHO</t>
+          <t>J. HAGENAERS COS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3386</v>
+        <v>-1.8537</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3372</v>
+        <v>-2.5024</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0014</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8351</v>
+        <v>-1.993</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7458</v>
+        <v>-2.3027</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.08939999999999999</v>
+        <v>0.3097</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.64</v>
+        <v>-1.8895</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6802</v>
+        <v>-2.0501</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0402</v>
+        <v>0.1606</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1951</v>
+        <v>-0.1035</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.2525</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1295</v>
+        <v>0.149</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9919</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1903</v>
+        <v>-2.1822</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1984</v>
+        <v>1.7855</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6949</v>
+        <v>0.1276</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4932</v>
+        <v>0.3629</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2017</v>
+        <v>-0.2353</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2065</v>
+        <v>0.4085</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2065</v>
+        <v>-0.7979000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. IRUELA RUBIO</t>
+          <t>R. SOLIVELLES MENDEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.392</v>
+        <v>-2.1675</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2344</v>
+        <v>-1.753</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1576</v>
+        <v>-0.4145</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.0513</v>
+        <v>-1.1076</v>
       </c>
       <c r="H23" t="n">
-        <v>-6.1633</v>
+        <v>-1.0584</v>
       </c>
       <c r="I23" t="n">
-        <v>4.112</v>
+        <v>-0.0492</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5397</v>
+        <v>-0.5797</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.557</v>
+        <v>-0.66</v>
       </c>
       <c r="L23" t="n">
-        <v>3.0172</v>
+        <v>0.0803</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.5115</v>
+        <v>-0.5279</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.6064</v>
+        <v>-0.3983</v>
       </c>
       <c r="O23" t="n">
-        <v>1.0948</v>
+        <v>-0.1295</v>
       </c>
       <c r="P23" t="n">
-        <v>1.5871</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.1984</v>
+        <v>-1.1903</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7855</v>
+        <v>0.1984</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2039</v>
+        <v>-0.068</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.4963</v>
+        <v>0.017</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2924</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.7239</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.7239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. SOLIVELLES MENDEZ</t>
+          <t>A. NEALE GIMENEZ-CASSINA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.4838</v>
+        <v>-2.5514</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9571</v>
+        <v>-3.3041</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5268</v>
+        <v>0.7527</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.1076</v>
+        <v>-1.517</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.0584</v>
+        <v>-0.7409</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0492</v>
+        <v>-0.7761</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5797</v>
+        <v>-2.0004</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.66</v>
+        <v>-0.6802</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0803</v>
+        <v>-1.3202</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5279</v>
+        <v>0.4835</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3983</v>
+        <v>-0.0607</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1295</v>
+        <v>0.5442</v>
       </c>
       <c r="P24" t="n">
         <v>-0.9919</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1903</v>
+        <v>-0.9919</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1984</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3843</v>
+        <v>-0.0425</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.187</v>
+        <v>-0.3117</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1973</v>
+        <v>0.2692</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. NEALE GIMENEZ-CASSINA</t>
+          <t>P. FEIXA MORANCHO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.7436</v>
+        <v>-2.8692</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.3041</v>
+        <v>-1.6433</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5605</v>
+        <v>-1.2259</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.517</v>
+        <v>-0.8351</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.7409</v>
+        <v>-0.7458</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.7761</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.0004</v>
+        <v>-0.64</v>
       </c>
       <c r="K25" t="n">
         <v>-0.6802</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.3202</v>
+        <v>0.0402</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4835</v>
+        <v>-0.1951</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.0607</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>0.5442</v>
+        <v>-0.1295</v>
       </c>
       <c r="P25" t="n">
         <v>-0.9919</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>0.1984</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2347</v>
+        <v>0.1644</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3117</v>
+        <v>0.1871</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0771</v>
+        <v>-0.0227</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="26">
@@ -2437,25 +2437,25 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-12.1814</v>
+        <v>-10.8211</v>
       </c>
       <c r="E26" t="n">
-        <v>-10.9931</v>
+        <v>-10.993</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.1887</v>
+        <v>0.1718000000000002</v>
       </c>
       <c r="G26" t="n">
-        <v>-7.145899999999999</v>
+        <v>-7.1459</v>
       </c>
       <c r="H26" t="n">
         <v>-11.1622</v>
       </c>
       <c r="I26" t="n">
-        <v>4.016</v>
+        <v>4.015999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>2.273400000000001</v>
+        <v>2.2734</v>
       </c>
       <c r="K26" t="n">
         <v>0.4604000000000005</v>
@@ -2482,22 +2482,22 @@
         <v>17.8547</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.5506</v>
+        <v>-1.1901</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.8207999999999999</v>
+        <v>-0.8209</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.7296</v>
+        <v>-0.3691</v>
       </c>
       <c r="V26" t="n">
-        <v>-3.476799999999999</v>
+        <v>-3.4768</v>
       </c>
       <c r="W26" t="n">
-        <v>4.417400000000001</v>
+        <v>4.4174</v>
       </c>
       <c r="X26" t="n">
-        <v>-7.8941</v>
+        <v>-7.894100000000001</v>
       </c>
     </row>
   </sheetData>
